--- a/01_analyses_states/Dadra and Nagar Haveli/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Dadra and Nagar Haveli/results/SoIB_summaries.xlsx
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C8">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">

--- a/01_analyses_states/Dadra and Nagar Haveli/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Dadra and Nagar Haveli/results/SoIB_summaries.xlsx
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C8">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2">
-        <v>94.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E2">
-        <v>95.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
